--- a/output/pdf_financials_xlsx/TCG.P.xlsx
+++ b/output/pdf_financials_xlsx/TCG.P.xlsx
@@ -3938,31 +3938,31 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.06975199999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6192,7 +6192,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -6706,7 +6710,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -7040,7 +7048,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -7508,7 +7520,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -7768,7 +7784,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -7896,7 +7916,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TCG.P.xlsx
+++ b/output/pdf_financials_xlsx/TCG.P.xlsx
@@ -1683,34 +1683,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.200449</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.363267</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.296452</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.13923</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.045732</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.009729</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002617</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002986</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003308</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.021329</v>
       </c>
     </row>
     <row r="35">
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.200449</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.363267</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.296452</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.13923</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.045732</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.009729</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002617</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002986</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.003308</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.021329</v>
       </c>
     </row>
     <row r="37">
@@ -2201,34 +2201,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.216949</v>
+        <v>0.0165</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.368267</v>
+        <v>0.005</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.296452</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.13923</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.069037</v>
+        <v>0.023305</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.011508</v>
+        <v>0.001779</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.352942</v>
+        <v>0.350325</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.423868</v>
+        <v>0.420882</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.494299</v>
+        <v>0.490991</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.582803</v>
+        <v>0.561474</v>
       </c>
     </row>
     <row r="49">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCG.P.xlsx
+++ b/output/pdf_financials_xlsx/TCG.P.xlsx
@@ -9550,7 +9550,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>0.233</v>
       </c>
